--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY-0930\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9840"/>
   </bookViews>
@@ -782,19 +787,19 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E7:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E1048576">
       <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F7:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F1048576">
       <formula1>"指定价格,限价指令,市价指令"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E1">
       <formula1>"买入,卖出,正回购,逆回购"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J5">
       <formula1>"数量,金额"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6 F1">
       <formula1>"限价指令,市价指令"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
@@ -783,23 +783,17 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E1048576">
-      <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F1048576">
-      <formula1>"指定价格,限价指令,市价指令"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
       <formula1>"买入,卖出,正回购,逆回购"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J5">
       <formula1>"数量,金额"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6 F1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576">
       <formula1>"限价指令,市价指令"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY-0930\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9840"/>
+    <workbookView windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>序号</t>
   </si>
@@ -48,15 +43,27 @@
     <t>收益率</t>
   </si>
   <si>
+    <t>目标类型</t>
+  </si>
+  <si>
     <t>指令数量</t>
   </si>
   <si>
     <t>指令金额</t>
   </si>
   <si>
+    <t>交易对手</t>
+  </si>
+  <si>
     <t>投资目的</t>
   </si>
   <si>
+    <t>对方席位</t>
+  </si>
+  <si>
+    <t>约定号</t>
+  </si>
+  <si>
     <t>开始日期</t>
   </si>
   <si>
@@ -72,45 +79,30 @@
     <t>限价指令</t>
   </si>
   <si>
-    <t>摊余成本类</t>
+    <t>数量</t>
   </si>
   <si>
     <t>123002.SH</t>
   </si>
   <si>
     <t>204007.SH</t>
-  </si>
-  <si>
-    <t>交易对手</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对方席位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>约定号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>数量</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,35 +115,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -159,35 +465,320 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -236,7 +827,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -271,7 +862,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -474,14 +1065,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -501,7 +1092,7 @@
     <col min="18" max="18" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" s="1" customFormat="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,34 +1121,34 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -568,28 +1159,25 @@
         <v>111111</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2">
         <v>3.56</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K2" s="4">
         <v>100000</v>
       </c>
       <c r="L2" s="5">
         <v>356000</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -600,7 +1188,7 @@
         <v>43962</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2</v>
       </c>
@@ -608,25 +1196,22 @@
         <v>10000</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2">
         <v>70</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K3" s="4">
         <v>1000</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -637,7 +1222,7 @@
         <v>43962</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>3</v>
       </c>
@@ -645,28 +1230,25 @@
         <v>10000</v>
       </c>
       <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2">
         <v>3.56</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K4" s="4">
         <v>1000</v>
       </c>
       <c r="L4" s="5">
         <v>100000</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -677,7 +1259,7 @@
         <v>43962</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>4</v>
       </c>
@@ -685,13 +1267,13 @@
         <v>10000</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2">
         <v>128</v>
@@ -703,16 +1285,13 @@
         <v>3.56</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K5" s="4">
         <v>10000</v>
       </c>
       <c r="L5" s="5">
         <v>128000</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -723,7 +1302,7 @@
         <v>43962</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>5</v>
       </c>
@@ -731,22 +1310,19 @@
         <v>10000</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2">
         <v>95</v>
       </c>
       <c r="K6" s="4">
         <v>1000</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -757,47 +1333,50 @@
         <v>43962</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="7" spans="15:16">
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="8" spans="15:16">
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="9" spans="15:16">
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="15:16">
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="11" spans="15:16">
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="15:16">
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N110">
+      <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 N111:N1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>"限价指令,市价指令"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"买入,卖出,正回购,逆回购"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J5">
       <formula1>"数量,金额"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576">
-      <formula1>"限价指令,市价指令"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\tams-3.0\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19815" windowHeight="7860"/>
+    <workbookView windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>序号</t>
   </si>
@@ -73,19 +68,26 @@
   </si>
   <si>
     <t>结束日期</t>
+  </si>
+  <si>
+    <t>申报类型</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
-    <numFmt numFmtId="178" formatCode="0.000_ "/>
-    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="181" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,21 +104,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -124,33 +450,319 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -437,14 +1049,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -464,7 +1076,7 @@
     <col min="18" max="18" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,40 +1131,46 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="15:16">
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="3" spans="15:16">
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="4" spans="15:16">
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="5" spans="15:16">
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="4">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S133">
+      <formula1>"不指定,意向申报,定价申报,点击成交申报,成交申报,收盘价固定价格申报,日均价固定价格申报"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 N104:N1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N103">
       <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
+      <formula1>"买入,卖出,正回购,逆回购"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"限价指令,市价指令"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
-      <formula1>"买入,卖出,正回购,逆回购"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
@@ -34,6 +34,9 @@
     <t>价格模式</t>
   </si>
   <si>
+    <t>申报类型</t>
+  </si>
+  <si>
     <t>指令价格</t>
   </si>
   <si>
@@ -68,9 +71,6 @@
   </si>
   <si>
     <t>结束日期</t>
-  </si>
-  <si>
-    <t>申报类型</t>
   </si>
 </sst>
 </file>
@@ -79,12 +79,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
   <fonts count="21">
@@ -111,6 +111,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -119,6 +127,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -133,8 +163,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,15 +173,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -158,29 +188,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,22 +228,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,6 +236,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,181 +263,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,6 +466,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -477,6 +488,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -499,50 +543,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -554,7 +554,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -566,146 +566,146 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1064,16 +1064,16 @@
     <col min="4" max="4" width="12.25" customWidth="1"/>
     <col min="5" max="5" width="11.625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.375" style="4" customWidth="1"/>
-    <col min="12" max="13" width="12.875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="14.875" customWidth="1"/>
-    <col min="15" max="16" width="12.5" customWidth="1"/>
-    <col min="17" max="17" width="13.25" customWidth="1"/>
-    <col min="18" max="18" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="4" customWidth="1"/>
+    <col min="13" max="14" width="12.875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
+    <col min="16" max="17" width="12.5" customWidth="1"/>
+    <col min="18" max="18" width="13.25" customWidth="1"/>
+    <col min="19" max="19" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:19">
@@ -1095,28 +1095,28 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -1135,31 +1135,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="15:16">
-      <c r="O2" s="1"/>
+    <row r="2" spans="16:17">
       <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="15:16">
-      <c r="O3" s="1"/>
+    <row r="3" spans="16:17">
       <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="15:16">
-      <c r="O4" s="1"/>
+    <row r="4" spans="16:17">
       <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="15:16">
-      <c r="O5" s="1"/>
+    <row r="5" spans="16:17">
       <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S133">
-      <formula1>"不指定,意向申报,定价申报,点击成交申报,成交申报,收盘价固定价格申报,日均价固定价格申报"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 N104:N1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 O104:O1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O103">
       <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
@@ -1168,6 +1165,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"限价指令,市价指令"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>"不指定"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeDzImport.xlsx
@@ -78,12 +78,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
@@ -105,12 +105,64 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -119,60 +171,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -181,14 +181,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -202,14 +194,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -226,23 +210,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,37 +257,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,7 +401,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,133 +425,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,6 +448,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -466,17 +475,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -488,21 +486,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,6 +508,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -542,9 +540,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -554,145 +554,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1152,12 +1152,15 @@
       <c r="Q5" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G309:G1048576">
+      <formula1>"不指定"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 O104:O1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O103">
-      <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G308">
+      <formula1>"不指定,意向申报,定价申报,点击成交申报,成交申报,收盘价固定价格申报,日均价固定价格申报"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"买入,卖出,正回购,逆回购"</formula1>
@@ -1165,8 +1168,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"限价指令,市价指令"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
-      <formula1>"不指定"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O103">
+      <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
